--- a/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/mrt_cp_table.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/mrt_cp_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.135673469387755</v>
+        <v>0.2357555555555556</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -479,16 +479,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9625</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0175438596491228</v>
+        <v>0.04947642536265798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.906578947368421</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="n">
-        <v>1.052631578947368</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.09787755102040815</v>
+        <v>0.1244444444444444</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9842105263157894</v>
+        <v>0.9125</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02723539420396496</v>
+        <v>0.04187448175467037</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8539473684210526</v>
+        <v>0.75</v>
       </c>
       <c r="H3" t="n">
-        <v>1.093421052631579</v>
+        <v>1.096875</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.07612244897959183</v>
+        <v>0.035</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.125</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9263157894736842</v>
+        <v>0.7875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03696720615036048</v>
+        <v>0.06468406123441676</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7315789473684211</v>
+        <v>0.528125</v>
       </c>
       <c r="H4" t="n">
-        <v>1.122368421052632</v>
+        <v>1.096875</v>
       </c>
     </row>
     <row r="5">
@@ -548,103 +548,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02285714285714287</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.125</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9368421052631579</v>
+        <v>0.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04949731922689785</v>
+        <v>0.06236095644623236</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6671052631578948</v>
+        <v>0.528125</v>
       </c>
       <c r="H5" t="n">
-        <v>1.146052631578947</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.01714285714285714</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9315789473684211</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0514785991267411</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.6552631578947368</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.146052631578947</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.01428571428571429</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9315789473684211</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0514785991267411</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.6552631578947368</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.146052631578947</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9315789473684211</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.0514785991267411</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.6552631578947368</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.146052631578947</v>
+        <v>1.096875</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/mrt_cp_table.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelA_CoreOnly/tables/mrt_cp_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2357555555555556</v>
+        <v>0.1431597076758367</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -479,16 +479,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9625</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04947642536265798</v>
+        <v>0.01960784313725491</v>
       </c>
       <c r="G2" t="n">
-        <v>0.75</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="H2" t="n">
-        <v>1.125</v>
+        <v>1.104411764705882</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1244444444444444</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.375</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9125</v>
+        <v>1.164705882352941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04187448175467037</v>
+        <v>0.05869266489057164</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75</v>
+        <v>0.863235294117647</v>
       </c>
       <c r="H3" t="n">
-        <v>1.096875</v>
+        <v>1.398529411764706</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.035</v>
+        <v>0.06293485135989885</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.125</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7875</v>
+        <v>1.18235294117647</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06468406123441676</v>
+        <v>0.05577044177775644</v>
       </c>
       <c r="G4" t="n">
-        <v>0.528125</v>
+        <v>0.863235294117647</v>
       </c>
       <c r="H4" t="n">
-        <v>1.096875</v>
+        <v>1.398529411764706</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,129 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.04629629629629629</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.125</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8</v>
+        <v>1.188235294117647</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06236095644623236</v>
+        <v>0.0445404576141198</v>
       </c>
       <c r="G5" t="n">
-        <v>0.528125</v>
+        <v>0.9220588235294117</v>
       </c>
       <c r="H5" t="n">
-        <v>1.096875</v>
+        <v>1.339705882352941</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.188235294117647</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04944909887419017</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9220588235294117</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.398529411764706</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0315126050420168</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.182352941176471</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05071575355442182</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9220588235294117</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.398529411764706</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0119047619047619</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.182352941176471</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0578015802862105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.863235294117647</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.398529411764706</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.182352941176471</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0578015802862105</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.863235294117647</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.398529411764706</v>
       </c>
     </row>
   </sheetData>
